--- a/data/phoneme_onset_C/St04_C.xlsx
+++ b/data/phoneme_onset_C/St04_C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/francesca_schiavon10_studio_unibo_it/Documents/Desktop/IMT/TESI/linguistic_pipeline_EEG/data/phoneme_onset_C/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="11_7025D3BDD3F059025B792811595ED87656C467DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29919C89-D524-488E-9F0F-B30D90B32EB3}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_7025D3BDD3F059025B792811595ED87656C467DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA7E5176-100D-4B39-99AE-1C6BF02CE90E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8867" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8867" uniqueCount="330">
   <si>
     <t>BEGIN</t>
   </si>
@@ -1024,6 +1024,9 @@
   <si>
     <t>dev'</t>
   </si>
+  <si>
+    <t>dz</t>
+  </si>
 </sst>
 </file>
 
@@ -1511,7 +1514,7 @@
         <v>104958</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -2454,7 +2457,7 @@
         <v>382347</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="C47" t="s">
         <v>46</v>
@@ -3489,7 +3492,7 @@
         <v>548604</v>
       </c>
       <c r="B92" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C92" t="s">
         <v>317</v>
@@ -4271,7 +4274,7 @@
         <v>736911</v>
       </c>
       <c r="B126" t="s">
-        <v>36</v>
+        <v>272</v>
       </c>
       <c r="C126" t="s">
         <v>77</v>
@@ -5559,7 +5562,7 @@
         <v>973728</v>
       </c>
       <c r="B182" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C182" t="s">
         <v>19</v>
@@ -5950,7 +5953,7 @@
         <v>1093239</v>
       </c>
       <c r="B199" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C199" t="s">
         <v>92</v>
@@ -6640,7 +6643,7 @@
         <v>1237446</v>
       </c>
       <c r="B229" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C229" t="s">
         <v>100</v>
@@ -6985,7 +6988,7 @@
         <v>1282428</v>
       </c>
       <c r="B244" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C244" t="s">
         <v>101</v>
@@ -9837,7 +9840,7 @@
         <v>1884803</v>
       </c>
       <c r="B368" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C368" t="s">
         <v>123</v>
@@ -10941,7 +10944,7 @@
         <v>2106657</v>
       </c>
       <c r="B416" t="s">
-        <v>135</v>
+        <v>329</v>
       </c>
       <c r="C416" t="s">
         <v>136</v>
@@ -11585,7 +11588,7 @@
         <v>2279529</v>
       </c>
       <c r="B444" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C444" t="s">
         <v>19</v>
@@ -12022,7 +12025,7 @@
         <v>2382282</v>
       </c>
       <c r="B463" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C463" t="s">
         <v>144</v>
@@ -12390,7 +12393,7 @@
         <v>2463867</v>
       </c>
       <c r="B479" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C479" t="s">
         <v>146</v>
@@ -12436,7 +12439,7 @@
         <v>2472687</v>
       </c>
       <c r="B481" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C481" t="s">
         <v>146</v>
@@ -13195,7 +13198,7 @@
         <v>2642031</v>
       </c>
       <c r="B514" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C514" t="s">
         <v>151</v>
@@ -13425,7 +13428,7 @@
         <v>2670255</v>
       </c>
       <c r="B524" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C524" t="s">
         <v>152</v>
@@ -13770,7 +13773,7 @@
         <v>2748753</v>
       </c>
       <c r="B539" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="C539" t="s">
         <v>155</v>
@@ -14000,7 +14003,7 @@
         <v>2833425</v>
       </c>
       <c r="B549" t="s">
-        <v>81</v>
+        <v>271</v>
       </c>
       <c r="C549" t="s">
         <v>157</v>
@@ -15012,7 +15015,7 @@
         <v>3040254</v>
       </c>
       <c r="B593" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C593" t="s">
         <v>164</v>
@@ -15840,7 +15843,7 @@
         <v>3220623</v>
       </c>
       <c r="B629" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C629" t="s">
         <v>168</v>
@@ -17151,7 +17154,7 @@
         <v>3450384</v>
       </c>
       <c r="B686" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C686" t="s">
         <v>179</v>
@@ -20440,7 +20443,7 @@
         <v>4160835</v>
       </c>
       <c r="B829" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C829" t="s">
         <v>196</v>
@@ -23660,7 +23663,7 @@
         <v>4792347</v>
       </c>
       <c r="B969" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C969" t="s">
         <v>19</v>
@@ -24258,7 +24261,7 @@
         <v>4947579</v>
       </c>
       <c r="B995" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C995" t="s">
         <v>322</v>
@@ -25730,7 +25733,7 @@
         <v>5226732</v>
       </c>
       <c r="B1059" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C1059" t="s">
         <v>19</v>
@@ -28513,7 +28516,7 @@
         <v>5794299</v>
       </c>
       <c r="B1180" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C1180" t="s">
         <v>239</v>
@@ -29893,7 +29896,7 @@
         <v>6057135</v>
       </c>
       <c r="B1240" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="C1240" t="s">
         <v>325</v>
@@ -30054,7 +30057,7 @@
         <v>6130782</v>
       </c>
       <c r="B1247" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C1247" t="s">
         <v>245</v>
@@ -30215,7 +30218,7 @@
         <v>6155478</v>
       </c>
       <c r="B1254" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C1254" t="s">
         <v>247</v>
@@ -30767,7 +30770,7 @@
         <v>6265728</v>
       </c>
       <c r="B1278" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C1278" t="s">
         <v>248</v>
@@ -31503,7 +31506,7 @@
         <v>6419196</v>
       </c>
       <c r="B1310" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C1310" t="s">
         <v>253</v>
@@ -31825,7 +31828,7 @@
         <v>6476967</v>
       </c>
       <c r="B1324" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C1324" t="s">
         <v>151</v>
@@ -32308,7 +32311,7 @@
         <v>6593391</v>
       </c>
       <c r="B1345" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C1345" t="s">
         <v>92</v>
@@ -32791,7 +32794,7 @@
         <v>6680709</v>
       </c>
       <c r="B1366" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C1366" t="s">
         <v>151</v>
@@ -35758,7 +35761,7 @@
         <v>7327215</v>
       </c>
       <c r="B1495" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C1495" t="s">
         <v>278</v>
@@ -35965,7 +35968,7 @@
         <v>7354557</v>
       </c>
       <c r="B1504" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="C1504" t="s">
         <v>279</v>
@@ -38219,7 +38222,7 @@
         <v>7852446</v>
       </c>
       <c r="B1602" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="C1602" t="s">
         <v>293</v>
@@ -38817,7 +38820,7 @@
         <v>7972839</v>
       </c>
       <c r="B1628" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C1628" t="s">
         <v>119</v>
@@ -40611,7 +40614,7 @@
         <v>8390025</v>
       </c>
       <c r="B1706" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C1706" t="s">
         <v>307</v>
@@ -40634,7 +40637,7 @@
         <v>8395758</v>
       </c>
       <c r="B1707" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C1707" t="s">
         <v>307</v>
@@ -40887,7 +40890,7 @@
         <v>8442504</v>
       </c>
       <c r="B1718" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C1718" t="s">
         <v>308</v>
@@ -41945,7 +41948,7 @@
         <v>8684613</v>
       </c>
       <c r="B1764" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C1764" t="s">
         <v>313</v>
